--- a/vga_data.xlsx
+++ b/vga_data.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\crawlVGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F13E5B-17AE-46A0-BF37-17BC794ECEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED5FFAB-DBBB-44EC-B8C4-E9A82532B26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{8B073BE8-E186-49A5-94FB-08EE197BD8F3}"/>
   </bookViews>
   <sheets>
     <sheet name="GPU Lookup" sheetId="1" r:id="rId1"/>
